--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260622.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260622.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -931,17 +931,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>162,000</t>
+          <t>5,220,520</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>5,220,520</t>
+          <t>162,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>10,447,121</t>
+          <t>370,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>923,659</t>
+          <t>10,447,121</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>370,000</t>
+          <t>923,659</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>490,000</t>
+          <t>4,389,578</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>4,389,578</t>
+          <t>1,359,384</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>1,359,384</t>
+          <t>490,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>3,429,981</t>
+          <t>2,559,703</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>2,559,703</t>
+          <t>3,429,981</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>202607WVHFN6F</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>179,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>202607WVHFN6F</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>2,159,107</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>179,000</t>
+          <t>2,159,107</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>793,000</t>
+          <t>92,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>92,000</t>
+          <t>793,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>988,121</t>
+          <t>384,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>384,000</t>
+          <t>988,121</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>154,000</t>
+          <t>175,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>326,000</t>
+          <t>1,732,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>1,732,000</t>
+          <t>154,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>175,000</t>
+          <t>326,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2163,17 +2163,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>70,000</t>
+          <t>113,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -2185,17 +2185,17 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>113,000</t>
+          <t>70,000</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -2239,6 +2239,24 @@
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>RDI_NTD</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>81,168,465</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
